--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD2A3C5-15A6-4D4D-9CA1-BBB86F08D41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377E01EF-1A82-4EFA-AB7C-52E5EFA486E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -280,6 +280,26 @@
   </si>
   <si>
     <t>https://x.com/ApricotLemonTea/status/2008523809998217337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://x.com/ApricotLemonTea/status/2025880968578670598</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>コミックマーケット108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comic Market 108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unconfirmed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -708,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -717,22 +737,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
+        <f t="shared" ref="G2:G3" si="0">FLOOR(C2/D2, 1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -740,41 +760,41 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G8" si="1">FLOOR(C3/D3, 1)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="G4:G9" si="1">FLOOR(C4/D4, 1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -783,7 +803,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="1"/>
@@ -792,10 +815,10 @@
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -803,11 +826,8 @@
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="1"/>
@@ -816,10 +836,10 @@
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -827,10 +847,12 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -838,10 +860,10 @@
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -849,36 +871,59 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
+    <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G8">
-    <sortCondition ref="G1:G8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
+    <sortCondition ref="G1:G9"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
-    <hyperlink ref="F2" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
+    <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31AE31C-89C8-41A9-900C-A2E47F7466A0}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -918,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -927,10 +972,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
@@ -939,10 +984,10 @@
     </row>
     <row r="3" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -950,41 +995,41 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G8" si="1">FLOOR(C3/D3, 1)</f>
+        <f t="shared" ref="G3" si="1">FLOOR(C3/D3, 1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="G4:G9" si="2">FLOOR(C4/D4, 1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -993,19 +1038,22 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1013,23 +1061,20 @@
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1037,57 +1082,82 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="2">
-        <f t="shared" si="1"/>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G8">
-    <sortCondition ref="G1:G8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
+    <sortCondition ref="G1:G9"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{9BEA0624-A66A-4722-9802-E6A4D673D124}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
-    <hyperlink ref="F2" r:id="rId3" xr:uid="{5BDFE10B-6F25-4C54-9DBF-09C9AB18661D}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{9BEA0624-A66A-4722-9802-E6A4D673D124}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{5BDFE10B-6F25-4C54-9DBF-09C9AB18661D}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{E6AA89AB-EFC6-492A-9673-4E3663E79A75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3546799F-72C6-45E7-B9AE-E5D18315E0B6}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -1127,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -1136,10 +1206,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
@@ -1148,10 +1218,10 @@
     </row>
     <row r="3" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -1159,41 +1229,41 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G8" si="1">FLOOR(C3/D3, 1)</f>
+        <f t="shared" ref="G3" si="1">FLOOR(C3/D3, 1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="G4:G9" si="2">FLOOR(C4/D4, 1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1202,19 +1272,22 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1222,23 +1295,20 @@
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1246,50 +1316,75 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="G7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="2">
-        <f t="shared" si="1"/>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G8">
-    <sortCondition ref="G1:G8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
+    <sortCondition ref="G1:G9"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{240A5452-EDA1-41CC-86F1-48A9EB0167F1}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
-    <hyperlink ref="F2" r:id="rId3" xr:uid="{ECB754AD-D93E-4319-A540-98B70F2DFFA3}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{240A5452-EDA1-41CC-86F1-48A9EB0167F1}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{ECB754AD-D93E-4319-A540-98B70F2DFFA3}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{A7D5620D-F248-465B-A374-8E1281D44884}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377E01EF-1A82-4EFA-AB7C-52E5EFA486E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8399CBD-15B4-4532-A963-C3DF04BC9459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,34 @@
     <author>Rui Yang</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{B44F684D-E6A9-4BBE-9B2A-8E46A740DB7C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 イベント
+2 開発
+3 旅行</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4E409F5E-4E6B-40A0-98BD-B6B4399D73F9}">
       <text>
         <r>
@@ -158,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,18 +228,9 @@
     <t>任务界面重做成游戏内的样式</t>
   </si>
   <si>
-    <t>動くLive2Dメモロビ</t>
-  </si>
-  <si>
-    <t>大厅Live2D动图</t>
-  </si>
-  <si>
     <t>Renewal tasks page to in-game style</t>
   </si>
   <si>
-    <t>Live2D memorial lobby</t>
-  </si>
-  <si>
     <t>2024-12-29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -300,6 +319,181 @@
   </si>
   <si>
     <t>Unconfirmed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メモロビリニューアル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>久留里線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小湊鉄道「里山トロッコ」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小海線「HIGH RAIL 星空」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>サンライズ瀬戸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大厅背景图重做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunrise Seto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Sunrise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>濑户</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>久留里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>小湊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铁道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「里山Torocco」</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>小海</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「HIGH RAIL 星空」</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>COSMIC PRINCESS KAGUYA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>！Pilgrimage</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「超时空辉夜姬！」圣地巡礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「超かぐや姫！」聖地巡礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kururi Line</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kominato-tetsudo Line「Satoyama Torocco」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Renewal background pictures of the top page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOKKAIDO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Koumi Line「HIGH RAIL Hoshizora」</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -307,7 +501,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +552,50 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -386,7 +624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -404,6 +642,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,11 +940,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
-    <col min="2" max="2" width="52.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="52.5" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
@@ -704,31 +957,31 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
+      <c r="B2" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -737,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G3" si="0">FLOOR(C2/D2, 1)</f>
+        <f>MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -751,8 +1004,8 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>30</v>
+      <c r="B3" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -761,22 +1014,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C3/D3, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -784,135 +1037,255 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="2">
-        <f t="shared" ref="G4:G9" si="1">FLOOR(C4/D4, 1)</f>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="4"/>
       <c r="G8" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="2">
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="2">
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <f>MIN(1, FLOOR(C11/D11, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <f>MIN(1, FLOOR(C12/D12, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2">
+        <f>MIN(1, FLOOR(C13/D13, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="2">
+        <f>MIN(1, FLOOR(C14/D14, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="1"/>
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2">
+        <f>MIN(1, FLOOR(C15/D15, 1))</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
-    <sortCondition ref="G1:G9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
+    <sortCondition ref="G1:G15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
-    <hyperlink ref="F9" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
+    <hyperlink ref="F15" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
+    <hyperlink ref="F11" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
     <hyperlink ref="F3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
     <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
   </hyperlinks>
@@ -923,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31AE31C-89C8-41A9-900C-A2E47F7466A0}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -946,16 +1319,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -963,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -972,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
+        <f>FLOOR(C2/D2, 1)</f>
         <v>0</v>
       </c>
     </row>
@@ -987,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -996,22 +1369,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3" si="1">FLOOR(C3/D3, 1)</f>
+        <f>FLOOR(C3/D3, 1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1019,134 +1392,254 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="2">
-        <f t="shared" ref="G4:G9" si="2">FLOOR(C4/D4, 1)</f>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
+      <c r="B8" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="4"/>
       <c r="G8" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="2">
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="2">
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <f>FLOOR(C11/D11, 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <f>FLOOR(C12/D12, 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2">
+        <f>FLOOR(C13/D13, 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="2">
+        <f>FLOOR(C14/D14, 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="2"/>
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2">
+        <f>FLOOR(C15/D15, 1)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
-    <sortCondition ref="G1:G9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
+    <sortCondition ref="G1:G15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{9BEA0624-A66A-4722-9802-E6A4D673D124}"/>
-    <hyperlink ref="F9" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{9BEA0624-A66A-4722-9802-E6A4D673D124}"/>
+    <hyperlink ref="F15" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{5BDFE10B-6F25-4C54-9DBF-09C9AB18661D}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{E6AA89AB-EFC6-492A-9673-4E3663E79A75}"/>
   </hyperlinks>
@@ -1157,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3546799F-72C6-45E7-B9AE-E5D18315E0B6}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -1180,16 +1673,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -1197,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -1206,10 +1699,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
@@ -1221,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -1230,10 +1723,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2">
         <f t="shared" ref="G3" si="1">FLOOR(C3/D3, 1)</f>
@@ -1242,10 +1735,10 @@
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1253,134 +1746,254 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="2">
-        <f t="shared" ref="G4:G9" si="2">FLOOR(C4/D4, 1)</f>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
+      <c r="B8" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="4"/>
       <c r="G8" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="2">
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="2">
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" ref="G11:G15" si="2">FLOOR(C11/D11, 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="2">
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G9">
-    <sortCondition ref="G1:G9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:G15">
+    <sortCondition ref="G1:G15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{240A5452-EDA1-41CC-86F1-48A9EB0167F1}"/>
-    <hyperlink ref="F9" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{240A5452-EDA1-41CC-86F1-48A9EB0167F1}"/>
+    <hyperlink ref="F15" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{ECB754AD-D93E-4319-A540-98B70F2DFFA3}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{A7D5620D-F248-465B-A374-8E1281D44884}"/>
   </hyperlinks>

--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8399CBD-15B4-4532-A963-C3DF04BC9459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF2FC94-E415-4D8A-BFB0-E84078698DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -55,8 +55,8 @@
           </rPr>
           <t xml:space="preserve">
 1 イベント
-2 開発
-3 旅行</t>
+2 旅行
+3 開発</t>
         </r>
       </text>
     </comment>
@@ -121,6 +121,60 @@
     <author>Rui Yang</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{C3787609-1F54-4B34-A97F-C8FB4F9B81CB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 イベント
+2 旅行
+3 開発</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{2547977F-895D-45BC-8760-0676C6A00AFE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G1" authorId="0" shapeId="0" xr:uid="{F9EF44DB-1743-498C-95D4-86DB6060EB7C}">
       <text>
         <r>
@@ -156,6 +210,60 @@
     <author>Rui Yang</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{5EE2926A-43B0-41BA-AAA8-270B71BA3185}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 イベント
+2 旅行
+3 開発</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{F2B71034-2226-4DE9-B0D2-1D8D092796F7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G1" authorId="0" shapeId="0" xr:uid="{5511642A-F0BC-4ECF-B8F1-68E02D3A44D2}">
       <text>
         <r>
@@ -1026,7 +1134,7 @@
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>40</v>
@@ -1046,7 +1154,7 @@
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>49</v>
@@ -1066,7 +1174,7 @@
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>36</v>
@@ -1086,7 +1194,7 @@
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>37</v>
@@ -1106,7 +1214,7 @@
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>35</v>
@@ -1124,7 +1232,7 @@
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>38</v>
@@ -1144,7 +1252,7 @@
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>39</v>
@@ -1188,7 +1296,7 @@
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>19</v>
@@ -1233,7 +1341,7 @@
     </row>
     <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>7</v>
@@ -1381,7 +1489,7 @@
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>43</v>
@@ -1401,7 +1509,7 @@
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
@@ -1421,7 +1529,7 @@
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>44</v>
@@ -1441,7 +1549,7 @@
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>45</v>
@@ -1461,7 +1569,7 @@
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>41</v>
@@ -1479,7 +1587,7 @@
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>38</v>
@@ -1499,7 +1607,7 @@
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>46</v>
@@ -1543,7 +1651,7 @@
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
@@ -1588,7 +1696,7 @@
     </row>
     <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
@@ -1735,7 +1843,7 @@
     </row>
     <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>42</v>
@@ -1755,7 +1863,7 @@
     </row>
     <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>47</v>
@@ -1775,7 +1883,7 @@
     </row>
     <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>50</v>
@@ -1795,7 +1903,7 @@
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>51</v>
@@ -1815,7 +1923,7 @@
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>52</v>
@@ -1833,7 +1941,7 @@
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>53</v>
@@ -1853,7 +1961,7 @@
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>54</v>
@@ -1897,7 +2005,7 @@
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
@@ -1942,7 +2050,7 @@
     </row>
     <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>11</v>

--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF2FC94-E415-4D8A-BFB0-E84078698DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA86CF-DEE0-4774-9E51-C1DBDA4404A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -604,12 +604,72 @@
     <t>Koumi Line「HIGH RAIL Hoshizora」</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>xxxまだ行ってないのよ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apricotlemontea.fanbox.cc/posts/7873164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxx还没去呢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxx漫画和照片册准备在同人展会上出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>xxx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>Haven't gone yet</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>xxx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>The report manga and photo book will release on events</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xxxレポ漫画と写真帳はイベントで出します</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -659,6 +719,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -752,19 +819,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,7 +1123,7 @@
     <col min="3" max="3" width="12.375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.875" style="2"/>
   </cols>
@@ -1146,7 +1213,9 @@
         <v>1</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="G4" s="2">
         <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
@@ -1166,7 +1235,9 @@
         <v>1</v>
       </c>
       <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="G5" s="2">
         <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
@@ -1186,7 +1257,9 @@
         <v>1</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="G6" s="2">
         <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
@@ -1206,7 +1279,9 @@
         <v>1</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="G7" s="2">
         <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
@@ -1243,8 +1318,12 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="G9" s="2">
         <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
@@ -1263,8 +1342,12 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="G10" s="2">
         <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
@@ -1396,9 +1479,10 @@
     <hyperlink ref="F11" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
     <hyperlink ref="F3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
     <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1411,7 +1495,7 @@
     <col min="2" max="2" width="52.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.875" style="2"/>
   </cols>
@@ -1501,7 +1585,9 @@
         <v>1</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="G4" s="2">
         <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
@@ -1521,7 +1607,9 @@
         <v>1</v>
       </c>
       <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="G5" s="2">
         <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
@@ -1541,7 +1629,9 @@
         <v>1</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="G6" s="2">
         <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
@@ -1561,7 +1651,9 @@
         <v>1</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="G7" s="2">
         <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
@@ -1598,8 +1690,12 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="G9" s="2">
         <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
@@ -1618,8 +1714,12 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="G10" s="2">
         <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
@@ -1750,9 +1850,10 @@
     <hyperlink ref="F15" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{5BDFE10B-6F25-4C54-9DBF-09C9AB18661D}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{E6AA89AB-EFC6-492A-9673-4E3663E79A75}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{F8171588-E755-4620-BEA5-0D87152B4788}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1765,7 +1866,7 @@
     <col min="2" max="2" width="52.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.875" style="2"/>
   </cols>
@@ -1855,7 +1956,9 @@
         <v>1</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="G4" s="2">
         <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
@@ -1875,7 +1978,9 @@
         <v>1</v>
       </c>
       <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="G5" s="2">
         <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
@@ -1895,7 +2000,9 @@
         <v>1</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="G6" s="2">
         <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
@@ -1915,7 +2022,9 @@
         <v>1</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="G7" s="2">
         <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
@@ -1952,8 +2061,12 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="G9" s="2">
         <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
@@ -1972,8 +2085,12 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="G10" s="2">
         <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
@@ -2104,8 +2221,9 @@
     <hyperlink ref="F15" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{ECB754AD-D93E-4319-A540-98B70F2DFFA3}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{A7D5620D-F248-465B-A374-8E1281D44884}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{AD85990B-D720-4DF8-B996-B9F8F03074E7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA86CF-DEE0-4774-9E51-C1DBDA4404A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B06F5DD-59F6-456F-8BB5-88DA814448B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -422,14 +422,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>未定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unconfirmed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>メモロビリニューアル</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -439,10 +431,6 @@
   </si>
   <si>
     <t>小湊鉄道「里山トロッコ」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>北海道</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -597,10 +585,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HOKKAIDO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Koumi Line「HIGH RAIL Hoshizora」</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -662,6 +646,34 @@
   </si>
   <si>
     <t>2024-05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～北海道～</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～HOKKAIDO～</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-16 (?)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JR TOKYO Wide Pass（日立駅、日光、河口湖、すずらんの里、諏訪湖etc.）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apricotlemontea.fanbox.cc/posts/9162696</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JR TOKYO Wide Pass</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -799,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -834,6 +846,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1115,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -1165,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>30</v>
@@ -1204,7 +1217,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1214,7 +1227,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G4" s="2">
         <f>MIN(1, FLOOR(C4/D4, 1))</f>
@@ -1226,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1236,7 +1249,7 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2">
         <f>MIN(1, FLOOR(C5/D5, 1))</f>
@@ -1248,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -1258,7 +1271,7 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2">
         <f>MIN(1, FLOOR(C6/D6, 1))</f>
@@ -1270,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1280,7 +1293,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2">
         <f>MIN(1, FLOOR(C7/D7, 1))</f>
@@ -1292,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1310,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1319,10 +1332,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2">
         <f>MIN(1, FLOOR(C9/D9, 1))</f>
@@ -1331,22 +1344,22 @@
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G10" s="2">
         <f>MIN(1, FLOOR(C10/D10, 1))</f>
@@ -1355,10 +1368,10 @@
     </row>
     <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -1367,10 +1380,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2">
         <f>MIN(1, FLOOR(C11/D11, 1))</f>
@@ -1379,10 +1389,10 @@
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1391,7 +1401,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G12" s="2">
         <f>MIN(1, FLOOR(C12/D12, 1))</f>
@@ -1468,27 +1481,53 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2">
+        <f>MIN(1, FLOOR(C16/D16, 1))</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="G1:G15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="G2:G16"/>
+    <sortCondition descending="1" ref="E2:E16"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F13" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
     <hyperlink ref="F15" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
-    <hyperlink ref="F11" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
+    <hyperlink ref="F10" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
     <hyperlink ref="F3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
     <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
-    <hyperlink ref="F10" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
+    <hyperlink ref="F16" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{CCB4D208-72BB-4EC8-8CE0-E32D29C148A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31AE31C-89C8-41A9-900C-A2E47F7466A0}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -1537,13 +1576,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f>FLOOR(C2/D2, 1)</f>
+        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1567,7 +1606,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f>FLOOR(C3/D3, 1)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1576,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1586,10 +1625,10 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1598,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1608,10 +1647,10 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1620,7 +1659,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -1630,10 +1669,10 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1642,7 +1681,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1652,10 +1691,10 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1664,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1673,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1682,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1691,46 +1730,46 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -1739,22 +1778,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f>FLOOR(C11/D11, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1763,10 +1799,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f>FLOOR(C12/D12, 1)</f>
+        <f>MIN(1, FLOOR(C12/D12, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1790,7 +1829,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f>FLOOR(C13/D13, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1812,7 +1851,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f>FLOOR(C14/D14, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1836,13 +1875,38 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f>FLOOR(C15/D15, 1)</f>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="G1:G15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="G2:G16"/>
+    <sortCondition descending="1" ref="E2:E16"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -1850,16 +1914,17 @@
     <hyperlink ref="F15" r:id="rId2" xr:uid="{3F86E828-B315-4C62-8B68-CB46CA9A5A11}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{5BDFE10B-6F25-4C54-9DBF-09C9AB18661D}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{E6AA89AB-EFC6-492A-9673-4E3663E79A75}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{F8171588-E755-4620-BEA5-0D87152B4788}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{F8171588-E755-4620-BEA5-0D87152B4788}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{F706B328-0AF8-4558-BE59-6F171092B52C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3546799F-72C6-45E7-B9AE-E5D18315E0B6}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
@@ -1908,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2" si="0">FLOOR(C2/D2, 1)</f>
+        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1938,7 +2003,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3" si="1">FLOOR(C3/D3, 1)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1947,7 +2012,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -1957,10 +2022,10 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1969,7 +2034,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1979,10 +2044,10 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1991,7 +2056,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -2001,10 +2066,10 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2013,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -2023,10 +2088,10 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2035,7 +2100,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -2044,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2053,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -2062,46 +2127,46 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -2110,22 +2175,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" ref="G11:G15" si="2">FLOOR(C11/D11, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -2134,10 +2196,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="2"/>
+        <f>MIN(1, FLOOR(C12/D12, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2161,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2183,7 +2248,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2207,13 +2272,38 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:G15">
-    <sortCondition ref="G1:G15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="G2:G16"/>
+    <sortCondition descending="1" ref="E2:E16"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -2221,9 +2311,10 @@
     <hyperlink ref="F15" r:id="rId2" xr:uid="{7F4F22C8-A15F-4693-B9D8-C10CADE1CE28}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{ECB754AD-D93E-4319-A540-98B70F2DFFA3}"/>
     <hyperlink ref="F2" r:id="rId4" xr:uid="{A7D5620D-F248-465B-A374-8E1281D44884}"/>
-    <hyperlink ref="F10" r:id="rId5" xr:uid="{AD85990B-D720-4DF8-B996-B9F8F03074E7}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{AD85990B-D720-4DF8-B996-B9F8F03074E7}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{AA406A99-F6AE-4C33-BC58-8D834E2A1464}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B06F5DD-59F6-456F-8BB5-88DA814448B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07800B3-5B90-45F7-AEA8-C3E034528A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -1184,7 +1184,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f>MIN(1, FLOOR(C2/D2, 1))</f>
+        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f>MIN(1, FLOOR(C3/D3, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         <v>51</v>
       </c>
       <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>51</v>
       </c>
       <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1308,13 +1308,13 @@
         <v>33</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         <v>57</v>
       </c>
       <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f>MIN(1, FLOOR(C11/D11, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
         <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f>MIN(1, FLOOR(C12/D12, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f>MIN(1, FLOOR(C13/D13, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f>MIN(1, FLOOR(C14/D14, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f>MIN(1, FLOOR(C15/D15, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f>MIN(1, FLOOR(C16/D16, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -2103,7 +2103,7 @@
         <v>49</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>

--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07800B3-5B90-45F7-AEA8-C3E034528A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C781E82-6836-4EEC-A9C7-C097EF4B2DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -674,6 +674,14 @@
   </si>
   <si>
     <t>JR TOKYO Wide Pass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://x.com/ApricotLemonTea/status/2030091730322923713</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1184,7 +1192,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
+        <f>MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1208,7 +1216,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C3/D3, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1230,7 +1238,7 @@
         <v>51</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1238,8 +1246,8 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>46</v>
+      <c r="B5" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1252,7 +1260,7 @@
         <v>51</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1261,7 +1269,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -1274,48 +1282,50 @@
         <v>51</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -1338,7 +1348,7 @@
         <v>57</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1362,7 +1372,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1383,7 +1393,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C11/D11, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1407,7 +1417,7 @@
         <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C12/D12, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1431,7 +1441,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C13/D13, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1453,7 +1463,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C14/D14, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1477,7 +1487,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C15/D15, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1501,7 +1511,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C16/D16, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1519,9 +1529,10 @@
     <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
     <hyperlink ref="F16" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
     <hyperlink ref="F12" r:id="rId7" xr:uid="{CCB4D208-72BB-4EC8-8CE0-E32D29C148A3}"/>
+    <hyperlink ref="F8" r:id="rId8" xr:uid="{79826DD5-1904-493F-9B84-9E527956FC03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId8"/>
+  <legacyDrawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1582,7 +1593,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
+        <f>MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1606,7 +1617,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C3/D3, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1628,7 +1639,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1636,8 +1647,8 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>45</v>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1650,7 +1661,7 @@
         <v>53</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1659,7 +1670,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -1672,48 +1683,50 @@
         <v>53</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -1736,7 +1749,7 @@
         <v>54</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1760,7 +1773,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1781,7 +1794,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C11/D11, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1829,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C13/D13, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1851,7 +1864,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C14/D14, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1875,7 +1888,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C15/D15, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1899,7 +1912,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C16/D16, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -1916,9 +1929,10 @@
     <hyperlink ref="F2" r:id="rId4" xr:uid="{E6AA89AB-EFC6-492A-9673-4E3663E79A75}"/>
     <hyperlink ref="F16" r:id="rId5" xr:uid="{F8171588-E755-4620-BEA5-0D87152B4788}"/>
     <hyperlink ref="F12" r:id="rId6" xr:uid="{F706B328-0AF8-4558-BE59-6F171092B52C}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{09F50F0C-4344-48D4-843F-30A5E5E8432B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1979,7 +1993,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
+        <f>MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -2003,7 +2017,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C3/D3, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -2025,7 +2039,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C4/D4, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -2033,8 +2047,8 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>44</v>
+      <c r="B5" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -2047,7 +2061,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C5/D5, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -2056,7 +2070,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -2069,48 +2083,50 @@
         <v>55</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C6/D6, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C7/D7, 1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="C8" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -2133,7 +2149,7 @@
         <v>56</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C9/D9, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2157,7 +2173,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C10/D10, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2178,7 +2194,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C11/D11, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2226,7 +2242,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C13/D13, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2248,7 +2264,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C14/D14, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2272,7 +2288,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C15/D15, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2296,7 +2312,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(1, FLOOR(C16/D16, 1))</f>
         <v>1</v>
       </c>
     </row>
@@ -2313,8 +2329,9 @@
     <hyperlink ref="F2" r:id="rId4" xr:uid="{A7D5620D-F248-465B-A374-8E1281D44884}"/>
     <hyperlink ref="F16" r:id="rId5" xr:uid="{AD85990B-D720-4DF8-B996-B9F8F03074E7}"/>
     <hyperlink ref="F12" r:id="rId6" xr:uid="{AA406A99-F6AE-4C33-BC58-8D834E2A1464}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{8B81EB7E-EF9A-4ADB-BE0B-BD42D6F539B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/public/data/mission.xlsx
+++ b/public/data/mission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C781E82-6836-4EEC-A9C7-C097EF4B2DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9C1312-60A4-43F0-B5DD-3CE55E2540F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4E409F5E-4E6B-40A0-98BD-B6B4399D73F9}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{4E409F5E-4E6B-40A0-98BD-B6B4399D73F9}">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,59 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{7C6BB744-4B1F-45B2-B183-247CE55D5716}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{2F7FE0E3-866B-4B04-9592-74B0AC713559}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{7720521B-3555-4BA5-A6D4-D9C27619126A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Rui Yang:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+设置为xxx开头的字符串则会在点击时显示xxx后的文本信息提示</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{7C6BB744-4B1F-45B2-B183-247CE55D5716}">
       <text>
         <r>
           <rPr>
@@ -294,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="72">
   <si>
     <t>tagIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -682,6 +734,18 @@
   </si>
   <si>
     <t>https://x.com/ApricotLemonTea/status/2030091730322923713</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titleZh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titleJa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titleEn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1136,403 +1200,597 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
     <col min="2" max="2" width="52.5" style="8" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="2"/>
+    <col min="3" max="4" width="52.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16" style="2" customWidth="1"/>
+    <col min="8" max="8" width="48.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2">
-        <f>MIN(1, FLOOR(C2/D2, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="2">
+        <f t="shared" ref="K2:K16" si="0">MIN(1, FLOOR(E2/F2, 1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="2">
-        <f>MIN(1, FLOOR(C3/D3, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="C5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2">
         <v>0.15</v>
       </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="C8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="C9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="2">
-        <f>MIN(1, FLOOR(C11/D11, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K11" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="C12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="H12" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="2">
-        <f>MIN(1, FLOOR(C12/D12, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="2">
-        <f>MIN(1, FLOOR(C13/D13, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>3</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="2">
-        <f>MIN(1, FLOOR(C14/D14, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="2">
-        <f>MIN(1, FLOOR(C15/D15, 1))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="C16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="2">
-        <f>MIN(1, FLOOR(C16/D16, 1))</f>
+      <c r="I16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
-    <sortCondition ref="G2:G16"/>
-    <sortCondition descending="1" ref="E2:E16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K16">
+    <sortCondition ref="K2:K16"/>
+    <sortCondition descending="1" ref="G2:G16"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F13" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
-    <hyperlink ref="F15" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
-    <hyperlink ref="F10" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
-    <hyperlink ref="F2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
-    <hyperlink ref="F16" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
-    <hyperlink ref="F12" r:id="rId7" xr:uid="{CCB4D208-72BB-4EC8-8CE0-E32D29C148A3}"/>
-    <hyperlink ref="F8" r:id="rId8" xr:uid="{79826DD5-1904-493F-9B84-9E527956FC03}"/>
+    <hyperlink ref="H13" r:id="rId1" xr:uid="{8D394F15-AE70-4076-8429-1743A563ECD9}"/>
+    <hyperlink ref="H15" r:id="rId2" xr:uid="{56C17B09-920A-4E32-B055-E862B78C3D3E}"/>
+    <hyperlink ref="H10" r:id="rId3" xr:uid="{C6A8C9A3-3A18-4BCB-82B6-1FCA8F3731D3}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{37DB8F46-A0B8-492A-83B8-5FE670536A4C}"/>
+    <hyperlink ref="H2" r:id="rId5" xr:uid="{4450AA0A-EB1F-49D2-B26B-7653A122C009}"/>
+    <hyperlink ref="H16" r:id="rId6" xr:uid="{8339C45A-0D45-4FD3-985C-1F1974AA7FDA}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{CCB4D208-72BB-4EC8-8CE0-E32D29C148A3}"/>
+    <hyperlink ref="H8" r:id="rId8" xr:uid="{79826DD5-1904-493F-9B84-9E527956FC03}"/>
+    <hyperlink ref="I13" r:id="rId9" xr:uid="{216FE969-9A9B-4560-BCF3-F5E866181A1B}"/>
+    <hyperlink ref="I15" r:id="rId10" xr:uid="{4CC6BADA-1A54-4B8D-AEB6-C56A85EB03F9}"/>
+    <hyperlink ref="I3" r:id="rId11" xr:uid="{48B1C874-BEC8-4EC1-8493-E719CF85B986}"/>
+    <hyperlink ref="I2" r:id="rId12" xr:uid="{C2446C34-0C66-492A-8DA8-8D749E7D63EF}"/>
+    <hyperlink ref="I16" r:id="rId13" xr:uid="{E7FA3EC4-D913-40C7-AEE9-CF056C0566B1}"/>
+    <hyperlink ref="I12" r:id="rId14" xr:uid="{7AE70218-A52E-4B67-8371-29367C2E52A6}"/>
+    <hyperlink ref="I8" r:id="rId15" xr:uid="{02AFCE9F-24E0-437E-B6AE-CC51C5C2B015}"/>
+    <hyperlink ref="J13" r:id="rId16" xr:uid="{74F815D4-3043-425F-8F9F-DA95D833ED6F}"/>
+    <hyperlink ref="J15" r:id="rId17" xr:uid="{9BC7BEFB-6870-42B1-B2E2-CE986C197896}"/>
+    <hyperlink ref="J3" r:id="rId18" xr:uid="{DED4B646-1F28-4E7F-AB34-CE85CC7D5787}"/>
+    <hyperlink ref="J2" r:id="rId19" xr:uid="{7816238E-0B3A-4253-B1BC-B0165DAE3BA1}"/>
+    <hyperlink ref="J16" r:id="rId20" xr:uid="{5103FCD1-21B1-4EAF-A117-AE3E51B1015B}"/>
+    <hyperlink ref="J12" r:id="rId21" xr:uid="{169A144E-B05F-4CAC-9391-4F7B0659C8F1}"/>
+    <hyperlink ref="J8" r:id="rId22" xr:uid="{B127D0F7-71C9-44BD-B1AA-94B2817A0B34}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId23"/>
+  <legacyDrawing r:id="rId24"/>
 </worksheet>
 </file>
 
@@ -1593,7 +1851,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f>MIN(1, FLOOR(C2/D2, 1))</f>
+        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -1617,7 +1875,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f>MIN(1, FLOOR(C3/D3, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1639,7 +1897,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1661,7 +1919,7 @@
         <v>53</v>
       </c>
       <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1683,7 +1941,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1701,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1725,7 +1983,7 @@
         <v>68</v>
       </c>
       <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1749,7 +2007,7 @@
         <v>54</v>
       </c>
       <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1773,7 +2031,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1794,7 +2052,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f>MIN(1, FLOOR(C11/D11, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1818,7 +2076,7 @@
         <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f>MIN(1, FLOOR(C12/D12, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1842,7 +2100,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f>MIN(1, FLOOR(C13/D13, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1864,7 +2122,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f>MIN(1, FLOOR(C14/D14, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1888,7 +2146,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f>MIN(1, FLOOR(C15/D15, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1912,7 +2170,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f>MIN(1, FLOOR(C16/D16, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1993,7 +2251,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <f>MIN(1, FLOOR(C2/D2, 1))</f>
+        <f t="shared" ref="G2:G16" si="0">MIN(1, FLOOR(C2/D2, 1))</f>
         <v>0</v>
       </c>
     </row>
@@ -2017,7 +2275,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="2">
-        <f>MIN(1, FLOOR(C3/D3, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2039,7 +2297,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="2">
-        <f>MIN(1, FLOOR(C4/D4, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2061,7 +2319,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="2">
-        <f>MIN(1, FLOOR(C5/D5, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2083,7 +2341,7 @@
         <v>55</v>
       </c>
       <c r="G6" s="2">
-        <f>MIN(1, FLOOR(C6/D6, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2101,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <f>MIN(1, FLOOR(C7/D7, 1))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2125,7 +2383,7 @@
         <v>68</v>
       </c>
       <c r="G8" s="2">
-        <f>MIN(1, FLOOR(C8/D8, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2149,7 +2407,7 @@
         <v>56</v>
       </c>
       <c r="G9" s="2">
-        <f>MIN(1, FLOOR(C9/D9, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2173,7 +2431,7 @@
         <v>26</v>
       </c>
       <c r="G10" s="2">
-        <f>MIN(1, FLOOR(C10/D10, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2194,7 +2452,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="2">
-        <f>MIN(1, FLOOR(C11/D11, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2218,7 +2476,7 @@
         <v>65</v>
       </c>
       <c r="G12" s="2">
-        <f>MIN(1, FLOOR(C12/D12, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2242,7 +2500,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <f>MIN(1, FLOOR(C13/D13, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2264,7 +2522,7 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="2">
-        <f>MIN(1, FLOOR(C14/D14, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2288,7 +2546,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="2">
-        <f>MIN(1, FLOOR(C15/D15, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2312,7 +2570,7 @@
         <v>52</v>
       </c>
       <c r="G16" s="2">
-        <f>MIN(1, FLOOR(C16/D16, 1))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
